--- a/academias/Electricidad - Estadisticos 20222.xlsx
+++ b/academias/Electricidad - Estadisticos 20222.xlsx
@@ -738,22 +738,25 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>74.19</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>25.81</v>
+      </c>
+      <c r="I8" s="2">
+        <v>6.8</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -840,22 +843,25 @@
         <v>29</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>75.86</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>24.14</v>
+      </c>
+      <c r="I11" s="2">
+        <v>6.6</v>
       </c>
       <c r="J11">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -884,13 +890,13 @@
         <v>27.27</v>
       </c>
       <c r="I12" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -907,22 +913,25 @@
         <v>30</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F13">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -939,22 +948,25 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8.9</v>
       </c>
       <c r="J14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2228,22 +2240,25 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>74.19</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>25.81</v>
+      </c>
+      <c r="I8" s="2">
+        <v>6.8</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2330,22 +2345,25 @@
         <v>29</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>75.86</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>24.14</v>
+      </c>
+      <c r="I11" s="2">
+        <v>6.6</v>
       </c>
       <c r="J11">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2374,13 +2392,13 @@
         <v>27.27</v>
       </c>
       <c r="I12" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2397,22 +2415,25 @@
         <v>30</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F13">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2429,22 +2450,25 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8.9</v>
       </c>
       <c r="J14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">

--- a/academias/Electricidad - Estadisticos 20222.xlsx
+++ b/academias/Electricidad - Estadisticos 20222.xlsx
@@ -1053,22 +1053,25 @@
         <v>33</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F17">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>27.27</v>
+      </c>
+      <c r="I17" s="2">
+        <v>6.6</v>
       </c>
       <c r="J17">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1085,22 +1088,25 @@
         <v>22</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F18">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>22.73</v>
+      </c>
+      <c r="I18" s="2">
+        <v>6.5</v>
       </c>
       <c r="J18">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1117,22 +1123,25 @@
         <v>22</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F19">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>22.73</v>
+      </c>
+      <c r="I19" s="2">
+        <v>6.1</v>
       </c>
       <c r="J19">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2555,22 +2564,25 @@
         <v>33</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F17">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>27.27</v>
+      </c>
+      <c r="I17" s="2">
+        <v>6.6</v>
       </c>
       <c r="J17">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2587,22 +2599,25 @@
         <v>22</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F18">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>22.73</v>
+      </c>
+      <c r="I18" s="2">
+        <v>6.5</v>
       </c>
       <c r="J18">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2619,22 +2634,25 @@
         <v>22</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F19">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>22.73</v>
+      </c>
+      <c r="I19" s="2">
+        <v>6.1</v>
       </c>
       <c r="J19">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">

--- a/academias/Electricidad - Estadisticos 20222.xlsx
+++ b/academias/Electricidad - Estadisticos 20222.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="35">
   <si>
     <t>Docente</t>
   </si>
@@ -51,15 +51,33 @@
     <t>Por_Blan</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Hernández Contreras Ángel</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
+    <t>Torres Sánchez José Luis</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
+    <t>6AEM</t>
+  </si>
+  <si>
     <t>2AEM</t>
   </si>
   <si>
@@ -69,43 +87,40 @@
     <t>2AEV</t>
   </si>
   <si>
+    <t>4BEM</t>
+  </si>
+  <si>
+    <t>4AEV</t>
+  </si>
+  <si>
+    <t>6BEM</t>
+  </si>
+  <si>
     <t>4AEM</t>
   </si>
   <si>
-    <t>4BEM</t>
-  </si>
-  <si>
-    <t>4AEV</t>
-  </si>
-  <si>
-    <t>6AEM</t>
-  </si>
-  <si>
-    <t>6BEM</t>
-  </si>
-  <si>
     <t>6AEV</t>
   </si>
   <si>
+    <t>REALIZA MANTENIMIENTO EN EL SISTEMA DE DISTRIBUCIÓN DE ENERGÍA ELÉCTRICA</t>
+  </si>
+  <si>
+    <t>REALIZA MANTENIMIENTO EN SUBESTACIONES ELÉCTRICAS</t>
+  </si>
+  <si>
     <t>DISEÑA INSTALACIONES ELÉCTRICAS</t>
   </si>
   <si>
+    <t>MANTIENE EN OPERACIÓN CIRCUITOS DE CONTROL ELECTROMAGNÉTICO</t>
+  </si>
+  <si>
     <t>REALIZA INSTALACIONES ELÉCTRICAS</t>
   </si>
   <si>
-    <t>MANTIENE EN OPERACIÓN CIRCUITOS DE CONTROL ELECTROMAGNÉTICO</t>
+    <t>PROGRAMA Y CONECTA CONTROLADORES LÓGICOS PROGRAMABLES (PLC´S)</t>
   </si>
   <si>
     <t>MANTIENE EN OPERACIÓN CIRCUITOS DE CONTROL ELECTRÓNICO</t>
-  </si>
-  <si>
-    <t>PROGRAMA Y CONECTA CONTROLADORES LÓGICOS PROGRAMABLES (PLC´S)</t>
-  </si>
-  <si>
-    <t>REALIZA MANTENIMIENTO EN EL SISTEMA DE DISTRIBUCIÓN DE ENERGÍA ELÉCTRICA</t>
-  </si>
-  <si>
-    <t>REALIZA MANTENIMIENTO EN SUBESTACIONES ELÉCTRICAS</t>
   </si>
 </sst>
 </file>
@@ -519,28 +534,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>91.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>8.82</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -554,28 +569,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -586,31 +601,31 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>86.48999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>13.51</v>
+        <v>8.82</v>
       </c>
       <c r="I4" s="2">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -621,31 +636,31 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>57.58</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>42.42</v>
+        <v>13.51</v>
       </c>
       <c r="I5" s="2">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -656,31 +671,31 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1">
-        <v>96.77</v>
+        <v>57.58</v>
       </c>
       <c r="H6" s="1">
-        <v>3.23</v>
+        <v>42.42</v>
       </c>
       <c r="I6" s="2">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -691,28 +706,28 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>96.77</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>3.23</v>
+        <v>6.9</v>
       </c>
       <c r="I7" s="2">
         <v>7.8</v>
@@ -726,31 +741,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" s="1">
-        <v>74.19</v>
+        <v>72.73</v>
       </c>
       <c r="H8" s="1">
-        <v>25.81</v>
+        <v>27.27</v>
       </c>
       <c r="I8" s="2">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -761,31 +776,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>93.09999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H9" s="1">
-        <v>6.9</v>
+        <v>5.88</v>
       </c>
       <c r="I9" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -796,31 +811,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>62.07</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>37.93</v>
+        <v>3.57</v>
       </c>
       <c r="I10" s="2">
-        <v>6.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -831,31 +846,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D11">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>75.86</v>
+        <v>74.19</v>
       </c>
       <c r="H11" s="1">
-        <v>24.14</v>
+        <v>25.81</v>
       </c>
       <c r="I11" s="2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -866,31 +881,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E12">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>72.73</v>
+        <v>75.86</v>
       </c>
       <c r="H12" s="1">
-        <v>27.27</v>
+        <v>24.14</v>
       </c>
       <c r="I12" s="2">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -901,31 +916,31 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D13">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E13">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>100</v>
+        <v>72.73</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>27.27</v>
       </c>
       <c r="I13" s="2">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -936,31 +951,31 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E14">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>100</v>
+        <v>77.27</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>22.73</v>
       </c>
       <c r="I14" s="2">
-        <v>8.9</v>
+        <v>6.5</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -971,31 +986,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E15">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1">
-        <v>89.29000000000001</v>
+        <v>77.27</v>
       </c>
       <c r="H15" s="1">
-        <v>10.71</v>
+        <v>22.73</v>
       </c>
       <c r="I15" s="2">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1006,31 +1021,31 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D16">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E16">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>96.43000000000001</v>
+        <v>96.77</v>
       </c>
       <c r="H16" s="1">
-        <v>3.57</v>
+        <v>3.23</v>
       </c>
       <c r="I16" s="2">
-        <v>9.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1041,31 +1056,31 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D17">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E17">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>72.73</v>
+        <v>96.77</v>
       </c>
       <c r="H17" s="1">
-        <v>27.27</v>
+        <v>3.23</v>
       </c>
       <c r="I17" s="2">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1076,31 +1091,31 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D18">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G18" s="1">
-        <v>77.27</v>
+        <v>62.07</v>
       </c>
       <c r="H18" s="1">
-        <v>22.73</v>
+        <v>37.93</v>
       </c>
       <c r="I18" s="2">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1111,31 +1126,31 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D19">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E19">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>77.27</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>22.73</v>
+        <v>10.71</v>
       </c>
       <c r="I19" s="2">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1146,13 +1161,13 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D20">
         <v>37</v>
@@ -1181,13 +1196,13 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D21">
         <v>33</v>
@@ -1216,13 +1231,13 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D22">
         <v>33</v>
@@ -1306,19 +1321,19 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -1327,7 +1342,7 @@
         <v>100</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K2" s="1">
         <v>100</v>
@@ -1338,19 +1353,19 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1359,7 +1374,7 @@
         <v>100</v>
       </c>
       <c r="J3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K3" s="1">
         <v>100</v>
@@ -1367,22 +1382,22 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -1391,7 +1406,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K4" s="1">
         <v>100</v>
@@ -1399,22 +1414,22 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -1423,7 +1438,7 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K5" s="1">
         <v>100</v>
@@ -1431,22 +1446,22 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1455,7 +1470,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -1463,22 +1478,22 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -1487,7 +1502,7 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -1495,22 +1510,22 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1519,7 +1534,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1527,22 +1542,22 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1551,7 +1566,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -1559,22 +1574,22 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1583,7 +1598,7 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1591,22 +1606,22 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D11">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1615,7 +1630,7 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -1623,22 +1638,22 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1647,7 +1662,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -1655,22 +1670,22 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D13">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -1679,7 +1694,7 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -1687,22 +1702,22 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -1711,7 +1726,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -1719,22 +1734,22 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -1743,7 +1758,7 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -1751,22 +1766,22 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D16">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -1775,7 +1790,7 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K16" s="1">
         <v>100</v>
@@ -1783,22 +1798,22 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D17">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -1807,7 +1822,7 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -1815,22 +1830,22 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D18">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -1839,7 +1854,7 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K18" s="1">
         <v>100</v>
@@ -1847,22 +1862,22 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D19">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -1871,7 +1886,7 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K19" s="1">
         <v>100</v>
@@ -1879,13 +1894,13 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D20">
         <v>37</v>
@@ -1911,13 +1926,13 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D21">
         <v>33</v>
@@ -1943,13 +1958,13 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D22">
         <v>33</v>
@@ -2030,28 +2045,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>91.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>8.82</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2065,28 +2080,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2097,31 +2112,31 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>86.48999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>13.51</v>
+        <v>8.82</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2132,31 +2147,31 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>57.58</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>42.42</v>
+        <v>13.51</v>
       </c>
       <c r="I5" s="2">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2167,31 +2182,31 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1">
-        <v>96.77</v>
+        <v>57.58</v>
       </c>
       <c r="H6" s="1">
-        <v>3.23</v>
+        <v>42.42</v>
       </c>
       <c r="I6" s="2">
-        <v>7.9</v>
+        <v>6.8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2202,31 +2217,31 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>96.77</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>3.23</v>
+        <v>6.9</v>
       </c>
       <c r="I7" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2237,31 +2252,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" s="1">
-        <v>74.19</v>
+        <v>72.73</v>
       </c>
       <c r="H8" s="1">
-        <v>25.81</v>
+        <v>27.27</v>
       </c>
       <c r="I8" s="2">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2272,31 +2287,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>93.09999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H9" s="1">
-        <v>6.9</v>
+        <v>5.88</v>
       </c>
       <c r="I9" s="2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2307,31 +2322,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>62.07</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>37.93</v>
+        <v>3.57</v>
       </c>
       <c r="I10" s="2">
-        <v>6.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2342,31 +2357,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D11">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>75.86</v>
+        <v>74.19</v>
       </c>
       <c r="H11" s="1">
-        <v>24.14</v>
+        <v>25.81</v>
       </c>
       <c r="I11" s="2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2377,31 +2392,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E12">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>72.73</v>
+        <v>75.86</v>
       </c>
       <c r="H12" s="1">
-        <v>27.27</v>
+        <v>24.14</v>
       </c>
       <c r="I12" s="2">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2412,31 +2427,31 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D13">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E13">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>100</v>
+        <v>72.73</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>27.27</v>
       </c>
       <c r="I13" s="2">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2447,31 +2462,31 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E14">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>100</v>
+        <v>77.27</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>22.73</v>
       </c>
       <c r="I14" s="2">
-        <v>8.9</v>
+        <v>6.5</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2482,31 +2497,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E15">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1">
-        <v>89.29000000000001</v>
+        <v>77.27</v>
       </c>
       <c r="H15" s="1">
-        <v>10.71</v>
+        <v>22.73</v>
       </c>
       <c r="I15" s="2">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2517,31 +2532,31 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D16">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E16">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>96.43000000000001</v>
+        <v>96.77</v>
       </c>
       <c r="H16" s="1">
-        <v>3.57</v>
+        <v>3.23</v>
       </c>
       <c r="I16" s="2">
-        <v>9.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2552,31 +2567,31 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D17">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E17">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>72.73</v>
+        <v>96.77</v>
       </c>
       <c r="H17" s="1">
-        <v>27.27</v>
+        <v>3.23</v>
       </c>
       <c r="I17" s="2">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2587,31 +2602,31 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D18">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G18" s="1">
-        <v>77.27</v>
+        <v>62.07</v>
       </c>
       <c r="H18" s="1">
-        <v>22.73</v>
+        <v>37.93</v>
       </c>
       <c r="I18" s="2">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2622,31 +2637,31 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D19">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E19">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>77.27</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>22.73</v>
+        <v>10.71</v>
       </c>
       <c r="I19" s="2">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2657,13 +2672,13 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D20">
         <v>37</v>
@@ -2692,13 +2707,13 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D21">
         <v>33</v>
@@ -2727,13 +2742,13 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D22">
         <v>33</v>

--- a/academias/Electricidad - Estadisticos 20222.xlsx
+++ b/academias/Electricidad - Estadisticos 20222.xlsx
@@ -8,25 +8,24 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="Final" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="36">
   <si>
     <t>Docente</t>
   </si>
   <si>
+    <t>Mat</t>
+  </si>
+  <si>
     <t>Grupo</t>
   </si>
   <si>
-    <t>Mat</t>
-  </si>
-  <si>
     <t>Totales</t>
   </si>
   <si>
@@ -36,10 +35,10 @@
     <t>Reprobados</t>
   </si>
   <si>
-    <t>Por_Apro</t>
-  </si>
-  <si>
-    <t>Por_Repro</t>
+    <t>por_aprobados</t>
+  </si>
+  <si>
+    <t>por_reprobados</t>
   </si>
   <si>
     <t>Promedio</t>
@@ -48,7 +47,7 @@
     <t>Blancos</t>
   </si>
   <si>
-    <t>Por_Blan</t>
+    <t>por_blancos</t>
   </si>
   <si>
     <t>Cruz Alejo José Armando</t>
@@ -69,12 +68,36 @@
     <t>Torres Sánchez José Luis</t>
   </si>
   <si>
+    <t>Total</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
+    <t>REALIZA MANTENIMIENTO EN EL SISTEMA DE DISTRIBUCIÓN DE ENERGÍA ELÉCTRICA</t>
+  </si>
+  <si>
+    <t>REALIZA MANTENIMIENTO EN SUBESTACIONES ELÉCTRICAS</t>
+  </si>
+  <si>
+    <t>DISEÑA INSTALACIONES ELÉCTRICAS</t>
+  </si>
+  <si>
+    <t>MANTIENE EN OPERACIÓN CIRCUITOS DE CONTROL ELECTROMAGNÉTICO</t>
+  </si>
+  <si>
+    <t>REALIZA INSTALACIONES ELÉCTRICAS</t>
+  </si>
+  <si>
+    <t>PROGRAMA Y CONECTA CONTROLADORES LÓGICOS PROGRAMABLES (PLC´S)</t>
+  </si>
+  <si>
+    <t>MANTIENE EN OPERACIÓN CIRCUITOS DE CONTROL ELECTRÓNICO</t>
+  </si>
+  <si>
     <t>6AEM</t>
   </si>
   <si>
@@ -100,27 +123,6 @@
   </si>
   <si>
     <t>6AEV</t>
-  </si>
-  <si>
-    <t>REALIZA MANTENIMIENTO EN EL SISTEMA DE DISTRIBUCIÓN DE ENERGÍA ELÉCTRICA</t>
-  </si>
-  <si>
-    <t>REALIZA MANTENIMIENTO EN SUBESTACIONES ELÉCTRICAS</t>
-  </si>
-  <si>
-    <t>DISEÑA INSTALACIONES ELÉCTRICAS</t>
-  </si>
-  <si>
-    <t>MANTIENE EN OPERACIÓN CIRCUITOS DE CONTROL ELECTROMAGNÉTICO</t>
-  </si>
-  <si>
-    <t>REALIZA INSTALACIONES ELÉCTRICAS</t>
-  </si>
-  <si>
-    <t>PROGRAMA Y CONECTA CONTROLADORES LÓGICOS PROGRAMABLES (PLC´S)</t>
-  </si>
-  <si>
-    <t>MANTIENE EN OPERACIÓN CIRCUITOS DE CONTROL ELECTRÓNICO</t>
   </si>
 </sst>
 </file>
@@ -484,11 +486,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -534,10 +536,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2">
         <v>30</v>
@@ -569,10 +571,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3">
         <v>30</v>
@@ -601,31 +603,25 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>91.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>8.82</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -639,28 +635,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>86.48999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="H5" s="1">
-        <v>13.51</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I5" s="2">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -677,25 +673,25 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>57.58</v>
+        <v>86.5</v>
       </c>
       <c r="H6" s="1">
-        <v>42.42</v>
+        <v>13.5</v>
       </c>
       <c r="I6" s="2">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -709,28 +705,28 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1">
-        <v>93.09999999999999</v>
+        <v>57.6</v>
       </c>
       <c r="H7" s="1">
-        <v>6.9</v>
+        <v>42.4</v>
       </c>
       <c r="I7" s="2">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -744,28 +740,28 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
         <v>31</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>72.73</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>27.27</v>
+        <v>6.9</v>
       </c>
       <c r="I8" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -776,31 +772,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
       </c>
       <c r="D9">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1">
-        <v>94.12</v>
+        <v>72.7</v>
       </c>
       <c r="H9" s="1">
-        <v>5.88</v>
+        <v>27.3</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -811,31 +807,25 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D10">
-        <v>28</v>
+        <v>166</v>
       </c>
       <c r="E10">
-        <v>27</v>
+        <v>133</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="G10" s="1">
-        <v>96.43000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>3.57</v>
+        <v>19.9</v>
       </c>
       <c r="I10" s="2">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -846,31 +836,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D11">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>74.19</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>25.81</v>
+        <v>5.9</v>
       </c>
       <c r="I11" s="2">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -881,31 +871,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
         <v>33</v>
       </c>
       <c r="D12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E12">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>75.86</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>24.14</v>
+        <v>3.6</v>
       </c>
       <c r="I12" s="2">
-        <v>6.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -916,31 +906,25 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="D13">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="E13">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>72.73</v>
+        <v>95.2</v>
       </c>
       <c r="H13" s="1">
-        <v>27.27</v>
+        <v>4.8</v>
       </c>
       <c r="I13" s="2">
-        <v>6.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -951,31 +935,31 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D14">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1">
-        <v>77.27</v>
+        <v>74.2</v>
       </c>
       <c r="H14" s="1">
-        <v>22.73</v>
+        <v>25.8</v>
       </c>
       <c r="I14" s="2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -986,31 +970,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15">
         <v>29</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>22</v>
       </c>
-      <c r="E15">
-        <v>17</v>
-      </c>
       <c r="F15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G15" s="1">
-        <v>77.27</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>22.73</v>
+        <v>24.1</v>
       </c>
       <c r="I15" s="2">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1021,31 +1005,25 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D16">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="E16">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G16" s="1">
-        <v>96.77</v>
+        <v>75</v>
       </c>
       <c r="H16" s="1">
-        <v>3.23</v>
+        <v>25</v>
       </c>
       <c r="I16" s="2">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1056,31 +1034,31 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D17">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E17">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G17" s="1">
-        <v>96.77</v>
+        <v>72.7</v>
       </c>
       <c r="H17" s="1">
-        <v>3.23</v>
+        <v>27.3</v>
       </c>
       <c r="I17" s="2">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1091,31 +1069,31 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1">
-        <v>62.07</v>
+        <v>77.3</v>
       </c>
       <c r="H18" s="1">
-        <v>37.93</v>
+        <v>22.7</v>
       </c>
       <c r="I18" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1126,31 +1104,31 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19">
+        <v>22</v>
+      </c>
+      <c r="E19">
         <v>17</v>
       </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19">
-        <v>28</v>
-      </c>
-      <c r="E19">
-        <v>25</v>
-      </c>
       <c r="F19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
-        <v>89.29000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="H19" s="1">
-        <v>10.71</v>
+        <v>22.7</v>
       </c>
       <c r="I19" s="2">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -1161,31 +1139,25 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D20">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="E20">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G20" s="1">
-        <v>86.48999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="H20" s="1">
-        <v>13.51</v>
+        <v>24.7</v>
       </c>
       <c r="I20" s="2">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1196,31 +1168,31 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D21">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E21">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F21">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>45.45</v>
+        <v>96.8</v>
       </c>
       <c r="H21" s="1">
-        <v>54.55</v>
+        <v>3.2</v>
       </c>
       <c r="I21" s="2">
-        <v>6.1</v>
+        <v>7.9</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1231,36 +1203,327 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
         <v>34</v>
       </c>
       <c r="D22">
+        <v>31</v>
+      </c>
+      <c r="E22">
+        <v>30</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>96.8</v>
+      </c>
+      <c r="H22" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="I22" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23">
+        <v>29</v>
+      </c>
+      <c r="E23">
+        <v>18</v>
+      </c>
+      <c r="F23">
+        <v>11</v>
+      </c>
+      <c r="G23" s="1">
+        <v>62.1</v>
+      </c>
+      <c r="H23" s="1">
+        <v>37.9</v>
+      </c>
+      <c r="I23" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24">
+        <v>91</v>
+      </c>
+      <c r="E24">
+        <v>78</v>
+      </c>
+      <c r="F24">
+        <v>13</v>
+      </c>
+      <c r="G24" s="1">
+        <v>85.7</v>
+      </c>
+      <c r="H24" s="1">
+        <v>14.3</v>
+      </c>
+      <c r="I24" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25">
+        <v>647</v>
+      </c>
+      <c r="E25">
+        <v>524</v>
+      </c>
+      <c r="F25">
+        <v>123</v>
+      </c>
+      <c r="G25" s="1">
+        <v>81</v>
+      </c>
+      <c r="H25" s="1">
+        <v>19</v>
+      </c>
+      <c r="I25" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" t="s">
         <v>33</v>
       </c>
-      <c r="E22">
+      <c r="D26">
+        <v>28</v>
+      </c>
+      <c r="E26">
+        <v>25</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26" s="1">
+        <v>89.3</v>
+      </c>
+      <c r="H26" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="I26" s="2">
+        <v>7.3</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27">
+        <v>28</v>
+      </c>
+      <c r="E27">
+        <v>25</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27" s="1">
+        <v>89.3</v>
+      </c>
+      <c r="H27" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="I27" s="2">
+        <v>7.3</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
         <v>19</v>
       </c>
-      <c r="F22">
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28">
+        <v>37</v>
+      </c>
+      <c r="E28">
+        <v>32</v>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+      <c r="G28" s="1">
+        <v>86.5</v>
+      </c>
+      <c r="H28" s="1">
+        <v>13.5</v>
+      </c>
+      <c r="I28" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29">
+        <v>33</v>
+      </c>
+      <c r="E29">
+        <v>15</v>
+      </c>
+      <c r="F29">
+        <v>18</v>
+      </c>
+      <c r="G29" s="1">
+        <v>45.5</v>
+      </c>
+      <c r="H29" s="1">
+        <v>54.5</v>
+      </c>
+      <c r="I29" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30">
+        <v>33</v>
+      </c>
+      <c r="E30">
+        <v>19</v>
+      </c>
+      <c r="F30">
         <v>14</v>
       </c>
-      <c r="G22" s="1">
-        <v>57.58</v>
-      </c>
-      <c r="H22" s="1">
-        <v>42.42</v>
-      </c>
-      <c r="I22" s="2">
+      <c r="G30" s="1">
+        <v>57.6</v>
+      </c>
+      <c r="H30" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="I30" s="2">
         <v>6.6</v>
       </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22" s="1">
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31">
+        <v>103</v>
+      </c>
+      <c r="E31">
+        <v>66</v>
+      </c>
+      <c r="F31">
+        <v>37</v>
+      </c>
+      <c r="G31" s="1">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="H31" s="1">
+        <v>35.9</v>
+      </c>
+      <c r="I31" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1271,11 +1534,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1321,31 +1584,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2">
         <v>30</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1353,63 +1619,63 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3">
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.9</v>
       </c>
       <c r="J3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1417,31 +1683,34 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>91.2</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1452,28 +1721,31 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>13.5</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1481,31 +1753,34 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>57.6</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>42.4</v>
+      </c>
+      <c r="I7" s="2">
+        <v>6.8</v>
       </c>
       <c r="J7">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1513,1265 +1788,790 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
         <v>31</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>6.9</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.9</v>
       </c>
       <c r="J8">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
       </c>
       <c r="D9">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>27.3</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.7</v>
       </c>
       <c r="J9">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D10">
-        <v>28</v>
+        <v>166</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F10">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>19.9</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.8</v>
       </c>
       <c r="J10">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D11">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>5.9</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8.1</v>
       </c>
       <c r="J11">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
         <v>33</v>
       </c>
       <c r="D12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>3.6</v>
+      </c>
+      <c r="I12" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J12">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="D13">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F13">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>4.8</v>
+      </c>
+      <c r="I13" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J13">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D14">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>74.2</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>25.8</v>
+      </c>
+      <c r="I14" s="2">
+        <v>6.8</v>
       </c>
       <c r="J14">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15">
         <v>29</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>22</v>
       </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
       <c r="F15">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>24.1</v>
+      </c>
+      <c r="I15" s="2">
+        <v>6.6</v>
       </c>
       <c r="J15">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D16">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F16">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I16" s="2">
+        <v>6.7</v>
       </c>
       <c r="J16">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D17">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F17">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>27.3</v>
+      </c>
+      <c r="I17" s="2">
+        <v>6.6</v>
       </c>
       <c r="J17">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F18">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>77.3</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>22.7</v>
+      </c>
+      <c r="I18" s="2">
+        <v>6.5</v>
       </c>
       <c r="J18">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19">
+        <v>22</v>
+      </c>
+      <c r="E19">
         <v>17</v>
       </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19">
-        <v>28</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
       <c r="F19">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>77.3</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>22.7</v>
+      </c>
+      <c r="I19" s="2">
+        <v>6.1</v>
       </c>
       <c r="J19">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D20">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F20">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>75.3</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>24.7</v>
+      </c>
+      <c r="I20" s="2">
+        <v>6.4</v>
       </c>
       <c r="J20">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D21">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F21">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>3.2</v>
+      </c>
+      <c r="I21" s="2">
+        <v>7.9</v>
       </c>
       <c r="J21">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
         <v>34</v>
       </c>
       <c r="D22">
+        <v>31</v>
+      </c>
+      <c r="E22">
+        <v>30</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>96.8</v>
+      </c>
+      <c r="H22" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="I22" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23">
+        <v>29</v>
+      </c>
+      <c r="E23">
+        <v>18</v>
+      </c>
+      <c r="F23">
+        <v>11</v>
+      </c>
+      <c r="G23" s="1">
+        <v>62.1</v>
+      </c>
+      <c r="H23" s="1">
+        <v>37.9</v>
+      </c>
+      <c r="I23" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24">
+        <v>91</v>
+      </c>
+      <c r="E24">
+        <v>78</v>
+      </c>
+      <c r="F24">
+        <v>13</v>
+      </c>
+      <c r="G24" s="1">
+        <v>85.7</v>
+      </c>
+      <c r="H24" s="1">
+        <v>14.3</v>
+      </c>
+      <c r="I24" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25">
+        <v>647</v>
+      </c>
+      <c r="E25">
+        <v>524</v>
+      </c>
+      <c r="F25">
+        <v>123</v>
+      </c>
+      <c r="G25" s="1">
+        <v>81</v>
+      </c>
+      <c r="H25" s="1">
+        <v>19</v>
+      </c>
+      <c r="I25" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" t="s">
         <v>33</v>
       </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
+      <c r="D26">
+        <v>28</v>
+      </c>
+      <c r="E26">
+        <v>25</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26" s="1">
+        <v>89.3</v>
+      </c>
+      <c r="H26" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="I26" s="2">
+        <v>7.3</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27">
+        <v>28</v>
+      </c>
+      <c r="E27">
+        <v>25</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27" s="1">
+        <v>89.3</v>
+      </c>
+      <c r="H27" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="I27" s="2">
+        <v>7.3</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28">
+        <v>37</v>
+      </c>
+      <c r="E28">
+        <v>32</v>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+      <c r="G28" s="1">
+        <v>86.5</v>
+      </c>
+      <c r="H28" s="1">
+        <v>13.5</v>
+      </c>
+      <c r="I28" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29">
         <v>33</v>
       </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>100</v>
-      </c>
-      <c r="J22">
+      <c r="E29">
+        <v>15</v>
+      </c>
+      <c r="F29">
+        <v>18</v>
+      </c>
+      <c r="G29" s="1">
+        <v>45.5</v>
+      </c>
+      <c r="H29" s="1">
+        <v>54.5</v>
+      </c>
+      <c r="I29" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30">
         <v>33</v>
       </c>
-      <c r="K22" s="1">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="1"/>
-    <col min="9" max="9" width="9.140625" style="2"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="E30">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2">
-        <v>30</v>
-      </c>
-      <c r="E2">
-        <v>30</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1">
-        <v>100</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>9</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="F30">
+        <v>14</v>
+      </c>
+      <c r="G30" s="1">
+        <v>57.6</v>
+      </c>
+      <c r="H30" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="I30" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3">
-        <v>30</v>
-      </c>
-      <c r="E3">
-        <v>30</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="1">
-        <v>100</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>8.9</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4">
-        <v>34</v>
-      </c>
-      <c r="E4">
-        <v>31</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4" s="1">
-        <v>91.18000000000001</v>
-      </c>
-      <c r="H4" s="1">
-        <v>8.82</v>
-      </c>
-      <c r="I4" s="2">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5">
+      <c r="D31">
+        <v>103</v>
+      </c>
+      <c r="E31">
+        <v>66</v>
+      </c>
+      <c r="F31">
         <v>37</v>
       </c>
-      <c r="E5">
-        <v>32</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5" s="1">
-        <v>86.48999999999999</v>
-      </c>
-      <c r="H5" s="1">
-        <v>13.51</v>
-      </c>
-      <c r="I5" s="2">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6">
-        <v>33</v>
-      </c>
-      <c r="E6">
-        <v>19</v>
-      </c>
-      <c r="F6">
-        <v>14</v>
-      </c>
-      <c r="G6" s="1">
-        <v>57.58</v>
-      </c>
-      <c r="H6" s="1">
-        <v>42.42</v>
-      </c>
-      <c r="I6" s="2">
+      <c r="G31" s="1">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="H31" s="1">
+        <v>35.9</v>
+      </c>
+      <c r="I31" s="2">
         <v>6.8</v>
       </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7">
-        <v>29</v>
-      </c>
-      <c r="E7">
-        <v>27</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7" s="1">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="H7" s="1">
-        <v>6.9</v>
-      </c>
-      <c r="I7" s="2">
-        <v>7.9</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8">
-        <v>33</v>
-      </c>
-      <c r="E8">
-        <v>24</v>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8" s="1">
-        <v>72.73</v>
-      </c>
-      <c r="H8" s="1">
-        <v>27.27</v>
-      </c>
-      <c r="I8" s="2">
-        <v>7.7</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9">
-        <v>34</v>
-      </c>
-      <c r="E9">
-        <v>32</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9" s="1">
-        <v>94.12</v>
-      </c>
-      <c r="H9" s="1">
-        <v>5.88</v>
-      </c>
-      <c r="I9" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10">
-        <v>28</v>
-      </c>
-      <c r="E10">
-        <v>27</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1">
-        <v>96.43000000000001</v>
-      </c>
-      <c r="H10" s="1">
-        <v>3.57</v>
-      </c>
-      <c r="I10" s="2">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11">
-        <v>31</v>
-      </c>
-      <c r="E11">
-        <v>23</v>
-      </c>
-      <c r="F11">
-        <v>8</v>
-      </c>
-      <c r="G11" s="1">
-        <v>74.19</v>
-      </c>
-      <c r="H11" s="1">
-        <v>25.81</v>
-      </c>
-      <c r="I11" s="2">
-        <v>6.8</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12">
-        <v>29</v>
-      </c>
-      <c r="E12">
-        <v>22</v>
-      </c>
-      <c r="F12">
-        <v>7</v>
-      </c>
-      <c r="G12" s="1">
-        <v>75.86</v>
-      </c>
-      <c r="H12" s="1">
-        <v>24.14</v>
-      </c>
-      <c r="I12" s="2">
-        <v>6.6</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13">
-        <v>33</v>
-      </c>
-      <c r="E13">
-        <v>24</v>
-      </c>
-      <c r="F13">
-        <v>9</v>
-      </c>
-      <c r="G13" s="1">
-        <v>72.73</v>
-      </c>
-      <c r="H13" s="1">
-        <v>27.27</v>
-      </c>
-      <c r="I13" s="2">
-        <v>6.6</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14">
-        <v>22</v>
-      </c>
-      <c r="E14">
-        <v>17</v>
-      </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-      <c r="G14" s="1">
-        <v>77.27</v>
-      </c>
-      <c r="H14" s="1">
-        <v>22.73</v>
-      </c>
-      <c r="I14" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15">
-        <v>22</v>
-      </c>
-      <c r="E15">
-        <v>17</v>
-      </c>
-      <c r="F15">
-        <v>5</v>
-      </c>
-      <c r="G15" s="1">
-        <v>77.27</v>
-      </c>
-      <c r="H15" s="1">
-        <v>22.73</v>
-      </c>
-      <c r="I15" s="2">
-        <v>6.1</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16">
-        <v>31</v>
-      </c>
-      <c r="E16">
-        <v>30</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" s="1">
-        <v>96.77</v>
-      </c>
-      <c r="H16" s="1">
-        <v>3.23</v>
-      </c>
-      <c r="I16" s="2">
-        <v>7.9</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17">
-        <v>31</v>
-      </c>
-      <c r="E17">
-        <v>30</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1">
-        <v>96.77</v>
-      </c>
-      <c r="H17" s="1">
-        <v>3.23</v>
-      </c>
-      <c r="I17" s="2">
-        <v>7.8</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18">
-        <v>29</v>
-      </c>
-      <c r="E18">
-        <v>18</v>
-      </c>
-      <c r="F18">
-        <v>11</v>
-      </c>
-      <c r="G18" s="1">
-        <v>62.07</v>
-      </c>
-      <c r="H18" s="1">
-        <v>37.93</v>
-      </c>
-      <c r="I18" s="2">
-        <v>6.9</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19">
-        <v>28</v>
-      </c>
-      <c r="E19">
-        <v>25</v>
-      </c>
-      <c r="F19">
-        <v>3</v>
-      </c>
-      <c r="G19" s="1">
-        <v>89.29000000000001</v>
-      </c>
-      <c r="H19" s="1">
-        <v>10.71</v>
-      </c>
-      <c r="I19" s="2">
-        <v>7.3</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20">
-        <v>37</v>
-      </c>
-      <c r="E20">
-        <v>32</v>
-      </c>
-      <c r="F20">
-        <v>5</v>
-      </c>
-      <c r="G20" s="1">
-        <v>86.48999999999999</v>
-      </c>
-      <c r="H20" s="1">
-        <v>13.51</v>
-      </c>
-      <c r="I20" s="2">
-        <v>7.6</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21">
-        <v>33</v>
-      </c>
-      <c r="E21">
-        <v>15</v>
-      </c>
-      <c r="F21">
-        <v>18</v>
-      </c>
-      <c r="G21" s="1">
-        <v>45.45</v>
-      </c>
-      <c r="H21" s="1">
-        <v>54.55</v>
-      </c>
-      <c r="I21" s="2">
-        <v>6.1</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22">
-        <v>33</v>
-      </c>
-      <c r="E22">
-        <v>19</v>
-      </c>
-      <c r="F22">
-        <v>14</v>
-      </c>
-      <c r="G22" s="1">
-        <v>57.58</v>
-      </c>
-      <c r="H22" s="1">
-        <v>42.42</v>
-      </c>
-      <c r="I22" s="2">
-        <v>6.6</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22" s="1">
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Electricidad - Estadisticos 20222.xlsx
+++ b/academias/Electricidad - Estadisticos 20222.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="37">
   <si>
     <t>Docente</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Torres Sánchez José Luis</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
@@ -83,6 +80,9 @@
     <t>REALIZA MANTENIMIENTO EN SUBESTACIONES ELÉCTRICAS</t>
   </si>
   <si>
+    <t>Totales Docente</t>
+  </si>
+  <si>
     <t>DISEÑA INSTALACIONES ELÉCTRICAS</t>
   </si>
   <si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>MANTIENE EN OPERACIÓN CIRCUITOS DE CONTROL ELECTRÓNICO</t>
+  </si>
+  <si>
+    <t>Totales Generales</t>
   </si>
   <si>
     <t>6AEM</t>
@@ -490,7 +493,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -536,10 +539,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>30</v>
@@ -571,10 +574,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>30</v>
@@ -605,6 +608,9 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
       <c r="D4">
         <v>60</v>
       </c>
@@ -638,7 +644,7 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>34</v>
@@ -673,7 +679,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6">
         <v>37</v>
@@ -708,7 +714,7 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7">
         <v>33</v>
@@ -743,7 +749,7 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8">
         <v>29</v>
@@ -778,7 +784,7 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9">
         <v>33</v>
@@ -809,6 +815,9 @@
       <c r="A10" t="s">
         <v>12</v>
       </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
       <c r="D10">
         <v>166</v>
       </c>
@@ -842,7 +851,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11">
         <v>34</v>
@@ -874,10 +883,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12">
         <v>28</v>
@@ -908,6 +917,9 @@
       <c r="A13" t="s">
         <v>13</v>
       </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
       <c r="D13">
         <v>62</v>
       </c>
@@ -941,7 +953,7 @@
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14">
         <v>31</v>
@@ -976,7 +988,7 @@
         <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D15">
         <v>29</v>
@@ -1007,6 +1019,9 @@
       <c r="A16" t="s">
         <v>14</v>
       </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
       <c r="D16">
         <v>60</v>
       </c>
@@ -1040,7 +1055,7 @@
         <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>33</v>
@@ -1072,10 +1087,10 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18">
         <v>22</v>
@@ -1107,10 +1122,10 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D19">
         <v>22</v>
@@ -1141,6 +1156,9 @@
       <c r="A20" t="s">
         <v>15</v>
       </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
       <c r="D20">
         <v>77</v>
       </c>
@@ -1174,7 +1192,7 @@
         <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D21">
         <v>31</v>
@@ -1209,7 +1227,7 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D22">
         <v>31</v>
@@ -1244,7 +1262,7 @@
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D23">
         <v>29</v>
@@ -1275,6 +1293,9 @@
       <c r="A24" t="s">
         <v>16</v>
       </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
       <c r="D24">
         <v>91</v>
       </c>
@@ -1304,23 +1325,29 @@
       <c r="A25" t="s">
         <v>17</v>
       </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
       <c r="D25">
-        <v>647</v>
+        <v>28</v>
       </c>
       <c r="E25">
-        <v>524</v>
+        <v>25</v>
       </c>
       <c r="F25">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="G25" s="1">
-        <v>81</v>
+        <v>89.3</v>
       </c>
       <c r="H25" s="1">
-        <v>19</v>
+        <v>10.7</v>
       </c>
       <c r="I25" s="2">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1331,13 +1358,10 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D26">
         <v>28</v>
@@ -1368,23 +1392,29 @@
       <c r="A27" t="s">
         <v>18</v>
       </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
       <c r="D27">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E27">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" s="1">
-        <v>89.3</v>
+        <v>86.5</v>
       </c>
       <c r="H27" s="1">
-        <v>10.7</v>
+        <v>13.5</v>
       </c>
       <c r="I27" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -1395,31 +1425,31 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
         <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D28">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E28">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G28" s="1">
-        <v>86.5</v>
+        <v>45.5</v>
       </c>
       <c r="H28" s="1">
-        <v>13.5</v>
+        <v>54.5</v>
       </c>
       <c r="I28" s="2">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -1430,31 +1460,31 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D29">
         <v>33</v>
       </c>
       <c r="E29">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F29">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G29" s="1">
-        <v>45.5</v>
+        <v>57.6</v>
       </c>
       <c r="H29" s="1">
-        <v>54.5</v>
+        <v>42.4</v>
       </c>
       <c r="I29" s="2">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1465,60 +1495,57 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30">
+        <v>103</v>
+      </c>
+      <c r="E30">
+        <v>66</v>
+      </c>
+      <c r="F30">
+        <v>37</v>
+      </c>
+      <c r="G30" s="1">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="H30" s="1">
+        <v>35.9</v>
+      </c>
+      <c r="I30" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31">
+        <v>647</v>
+      </c>
+      <c r="E31">
+        <v>524</v>
+      </c>
+      <c r="F31">
+        <v>123</v>
+      </c>
+      <c r="G31" s="1">
+        <v>81</v>
+      </c>
+      <c r="H31" s="1">
         <v>19</v>
       </c>
-      <c r="B30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30">
-        <v>33</v>
-      </c>
-      <c r="E30">
-        <v>19</v>
-      </c>
-      <c r="F30">
-        <v>14</v>
-      </c>
-      <c r="G30" s="1">
-        <v>57.6</v>
-      </c>
-      <c r="H30" s="1">
-        <v>42.4</v>
-      </c>
-      <c r="I30" s="2">
-        <v>6.6</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31">
-        <v>103</v>
-      </c>
-      <c r="E31">
-        <v>66</v>
-      </c>
-      <c r="F31">
-        <v>37</v>
-      </c>
-      <c r="G31" s="1">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="H31" s="1">
-        <v>35.9</v>
-      </c>
       <c r="I31" s="2">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -1584,10 +1611,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>30</v>
@@ -1619,10 +1646,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>30</v>
@@ -1653,6 +1680,9 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
       <c r="D4">
         <v>60</v>
       </c>
@@ -1686,7 +1716,7 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>34</v>
@@ -1721,7 +1751,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6">
         <v>37</v>
@@ -1756,7 +1786,7 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7">
         <v>33</v>
@@ -1791,7 +1821,7 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8">
         <v>29</v>
@@ -1826,7 +1856,7 @@
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9">
         <v>33</v>
@@ -1857,6 +1887,9 @@
       <c r="A10" t="s">
         <v>12</v>
       </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
       <c r="D10">
         <v>166</v>
       </c>
@@ -1890,7 +1923,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11">
         <v>34</v>
@@ -1922,10 +1955,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12">
         <v>28</v>
@@ -1956,6 +1989,9 @@
       <c r="A13" t="s">
         <v>13</v>
       </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
       <c r="D13">
         <v>62</v>
       </c>
@@ -1989,7 +2025,7 @@
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14">
         <v>31</v>
@@ -2024,7 +2060,7 @@
         <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D15">
         <v>29</v>
@@ -2055,6 +2091,9 @@
       <c r="A16" t="s">
         <v>14</v>
       </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
       <c r="D16">
         <v>60</v>
       </c>
@@ -2088,7 +2127,7 @@
         <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>33</v>
@@ -2120,10 +2159,10 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18">
         <v>22</v>
@@ -2155,10 +2194,10 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D19">
         <v>22</v>
@@ -2189,6 +2228,9 @@
       <c r="A20" t="s">
         <v>15</v>
       </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
       <c r="D20">
         <v>77</v>
       </c>
@@ -2222,7 +2264,7 @@
         <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D21">
         <v>31</v>
@@ -2257,7 +2299,7 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D22">
         <v>31</v>
@@ -2292,7 +2334,7 @@
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D23">
         <v>29</v>
@@ -2323,6 +2365,9 @@
       <c r="A24" t="s">
         <v>16</v>
       </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
       <c r="D24">
         <v>91</v>
       </c>
@@ -2352,23 +2397,29 @@
       <c r="A25" t="s">
         <v>17</v>
       </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
       <c r="D25">
-        <v>647</v>
+        <v>28</v>
       </c>
       <c r="E25">
-        <v>524</v>
+        <v>25</v>
       </c>
       <c r="F25">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="G25" s="1">
-        <v>81</v>
+        <v>89.3</v>
       </c>
       <c r="H25" s="1">
-        <v>19</v>
+        <v>10.7</v>
       </c>
       <c r="I25" s="2">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -2379,13 +2430,10 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D26">
         <v>28</v>
@@ -2416,23 +2464,29 @@
       <c r="A27" t="s">
         <v>18</v>
       </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
       <c r="D27">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E27">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" s="1">
-        <v>89.3</v>
+        <v>86.5</v>
       </c>
       <c r="H27" s="1">
-        <v>10.7</v>
+        <v>13.5</v>
       </c>
       <c r="I27" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -2443,31 +2497,31 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
         <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D28">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E28">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G28" s="1">
-        <v>86.5</v>
+        <v>45.5</v>
       </c>
       <c r="H28" s="1">
-        <v>13.5</v>
+        <v>54.5</v>
       </c>
       <c r="I28" s="2">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -2478,31 +2532,31 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D29">
         <v>33</v>
       </c>
       <c r="E29">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F29">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G29" s="1">
-        <v>45.5</v>
+        <v>57.6</v>
       </c>
       <c r="H29" s="1">
-        <v>54.5</v>
+        <v>42.4</v>
       </c>
       <c r="I29" s="2">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -2513,60 +2567,57 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30">
+        <v>103</v>
+      </c>
+      <c r="E30">
+        <v>66</v>
+      </c>
+      <c r="F30">
+        <v>37</v>
+      </c>
+      <c r="G30" s="1">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="H30" s="1">
+        <v>35.9</v>
+      </c>
+      <c r="I30" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31">
+        <v>647</v>
+      </c>
+      <c r="E31">
+        <v>524</v>
+      </c>
+      <c r="F31">
+        <v>123</v>
+      </c>
+      <c r="G31" s="1">
+        <v>81</v>
+      </c>
+      <c r="H31" s="1">
         <v>19</v>
       </c>
-      <c r="B30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30">
-        <v>33</v>
-      </c>
-      <c r="E30">
-        <v>19</v>
-      </c>
-      <c r="F30">
-        <v>14</v>
-      </c>
-      <c r="G30" s="1">
-        <v>57.6</v>
-      </c>
-      <c r="H30" s="1">
-        <v>42.4</v>
-      </c>
-      <c r="I30" s="2">
-        <v>6.6</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31">
-        <v>103</v>
-      </c>
-      <c r="E31">
-        <v>66</v>
-      </c>
-      <c r="F31">
-        <v>37</v>
-      </c>
-      <c r="G31" s="1">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="H31" s="1">
-        <v>35.9</v>
-      </c>
       <c r="I31" s="2">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="J31">
         <v>0</v>

--- a/academias/Electricidad - Estadisticos 20222.xlsx
+++ b/academias/Electricidad - Estadisticos 20222.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="Final" sheetId="2" r:id="rId2"/>
+    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="37">
   <si>
     <t>Docente</t>
   </si>
@@ -1620,6 +1621,1078 @@
         <v>30</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>30</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>30</v>
+      </c>
+      <c r="K2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>30</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>100</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>30</v>
+      </c>
+      <c r="K3" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4">
+        <v>60</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>60</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>100</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>60</v>
+      </c>
+      <c r="K4" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5">
+        <v>34</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>34</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>34</v>
+      </c>
+      <c r="K5" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6">
+        <v>37</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>37</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>37</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7">
+        <v>33</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>33</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>100</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>33</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8">
+        <v>29</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>29</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>29</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9">
+        <v>33</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>33</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>33</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10">
+        <v>166</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>166</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>100</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>166</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11">
+        <v>34</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>34</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>34</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12">
+        <v>28</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>28</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>28</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13">
+        <v>62</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>62</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>100</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>62</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14">
+        <v>31</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>31</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>100</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>31</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15">
+        <v>29</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>29</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>29</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16">
+        <v>60</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>60</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>100</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>60</v>
+      </c>
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17">
+        <v>33</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>33</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>100</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>33</v>
+      </c>
+      <c r="K17" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18">
+        <v>22</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>22</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>100</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>22</v>
+      </c>
+      <c r="K18" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19">
+        <v>22</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>22</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>100</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>22</v>
+      </c>
+      <c r="K19" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20">
+        <v>77</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>77</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>100</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>77</v>
+      </c>
+      <c r="K20" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21">
+        <v>31</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>31</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>100</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>31</v>
+      </c>
+      <c r="K21" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22">
+        <v>31</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>31</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>100</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>31</v>
+      </c>
+      <c r="K22" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23">
+        <v>29</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>29</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>100</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>29</v>
+      </c>
+      <c r="K23" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24">
+        <v>91</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>91</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>100</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>91</v>
+      </c>
+      <c r="K24" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25">
+        <v>28</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>28</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>100</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>28</v>
+      </c>
+      <c r="K25" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26">
+        <v>28</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>28</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>100</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>28</v>
+      </c>
+      <c r="K26" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27">
+        <v>37</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>37</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>100</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>37</v>
+      </c>
+      <c r="K27" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28">
+        <v>33</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>33</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>100</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>33</v>
+      </c>
+      <c r="K28" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29">
+        <v>33</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>33</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>100</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>33</v>
+      </c>
+      <c r="K29" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30">
+        <v>103</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>103</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>100</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>103</v>
+      </c>
+      <c r="K30" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31">
+        <v>647</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>647</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>100</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>647</v>
+      </c>
+      <c r="K31" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2">
         <v>30</v>
       </c>
       <c r="F2">

--- a/academias/Electricidad - Estadisticos 20222.xlsx
+++ b/academias/Electricidad - Estadisticos 20222.xlsx
@@ -1723,25 +1723,25 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>85.3</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>14.7</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J5">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1758,25 +1758,25 @@
         <v>37</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>70.3</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>29.7</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J6">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1828,25 +1828,25 @@
         <v>29</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>86.2</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>13.8</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1895,25 +1895,25 @@
         <v>166</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F10">
-        <v>166</v>
+        <v>86</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>48.2</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>51.8</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="J10">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2067,25 +2067,25 @@
         <v>29</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F15">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>86.2</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>13.8</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J15">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2099,25 +2099,25 @@
         <v>60</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F16">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>41.7</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J16">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2134,25 +2134,25 @@
         <v>33</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F17">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J17">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2169,25 +2169,25 @@
         <v>22</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F18">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>68.2</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>31.8</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J18">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2204,25 +2204,25 @@
         <v>22</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F19">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>77.3</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>22.7</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J19">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2236,25 +2236,25 @@
         <v>77</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F20">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>29.9</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J20">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2271,25 +2271,25 @@
         <v>31</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F21">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>6.5</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J21">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2306,25 +2306,25 @@
         <v>31</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F22">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>6.5</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J22">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2341,25 +2341,25 @@
         <v>29</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F23">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>58.6</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>41.4</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J23">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2373,25 +2373,25 @@
         <v>91</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F24">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>17.6</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J24">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2475,25 +2475,25 @@
         <v>37</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F27">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>89.2</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>10.8</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J27">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2510,25 +2510,25 @@
         <v>33</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F28">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>42.4</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>57.6</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J28">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2577,25 +2577,25 @@
         <v>103</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F30">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>45.6</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>54.4</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J30">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2606,25 +2606,25 @@
         <v>647</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="F31">
-        <v>647</v>
+        <v>366</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>43.4</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>56.6</v>
       </c>
       <c r="I31" s="2">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J31">
-        <v>647</v>
+        <v>280</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>43.3</v>
       </c>
     </row>
   </sheetData>
@@ -2795,16 +2795,16 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>91.2</v>
+        <v>85.3</v>
       </c>
       <c r="H5" s="1">
-        <v>8.800000000000001</v>
+        <v>14.7</v>
       </c>
       <c r="I5" s="2">
         <v>8.699999999999999</v>
@@ -2830,19 +2830,19 @@
         <v>37</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1">
-        <v>86.5</v>
+        <v>70.3</v>
       </c>
       <c r="H6" s="1">
-        <v>13.5</v>
+        <v>29.7</v>
       </c>
       <c r="I6" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2900,19 +2900,19 @@
         <v>29</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>93.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="H8" s="1">
-        <v>6.9</v>
+        <v>13.8</v>
       </c>
       <c r="I8" s="2">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2967,16 +2967,16 @@
         <v>166</v>
       </c>
       <c r="E10">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F10">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G10" s="1">
-        <v>80.09999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>19.9</v>
+        <v>25.9</v>
       </c>
       <c r="I10" s="2">
         <v>7.8</v>
@@ -3139,19 +3139,19 @@
         <v>29</v>
       </c>
       <c r="E15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>75.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="H15" s="1">
-        <v>24.1</v>
+        <v>13.8</v>
       </c>
       <c r="I15" s="2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3171,19 +3171,19 @@
         <v>60</v>
       </c>
       <c r="E16">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F16">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G16" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H16" s="1">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I16" s="2">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3206,19 +3206,19 @@
         <v>33</v>
       </c>
       <c r="E17">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G17" s="1">
-        <v>72.7</v>
+        <v>66.7</v>
       </c>
       <c r="H17" s="1">
-        <v>27.3</v>
+        <v>33.3</v>
       </c>
       <c r="I17" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3241,16 +3241,16 @@
         <v>22</v>
       </c>
       <c r="E18">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G18" s="1">
-        <v>77.3</v>
+        <v>68.2</v>
       </c>
       <c r="H18" s="1">
-        <v>22.7</v>
+        <v>31.8</v>
       </c>
       <c r="I18" s="2">
         <v>6.5</v>
@@ -3288,7 +3288,7 @@
         <v>22.7</v>
       </c>
       <c r="I19" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3308,19 +3308,19 @@
         <v>77</v>
       </c>
       <c r="E20">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F20">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G20" s="1">
-        <v>75.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>24.7</v>
+        <v>29.9</v>
       </c>
       <c r="I20" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3343,19 +3343,19 @@
         <v>31</v>
       </c>
       <c r="E21">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="1">
-        <v>96.8</v>
+        <v>93.5</v>
       </c>
       <c r="H21" s="1">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="I21" s="2">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3378,19 +3378,19 @@
         <v>31</v>
       </c>
       <c r="E22">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="1">
-        <v>96.8</v>
+        <v>93.5</v>
       </c>
       <c r="H22" s="1">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="I22" s="2">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3413,19 +3413,19 @@
         <v>29</v>
       </c>
       <c r="E23">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F23">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23" s="1">
-        <v>62.1</v>
+        <v>58.6</v>
       </c>
       <c r="H23" s="1">
-        <v>37.9</v>
+        <v>41.4</v>
       </c>
       <c r="I23" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3445,19 +3445,19 @@
         <v>91</v>
       </c>
       <c r="E24">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F24">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G24" s="1">
-        <v>85.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H24" s="1">
-        <v>14.3</v>
+        <v>17.6</v>
       </c>
       <c r="I24" s="2">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3547,19 +3547,19 @@
         <v>37</v>
       </c>
       <c r="E27">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="1">
-        <v>86.5</v>
+        <v>89.2</v>
       </c>
       <c r="H27" s="1">
-        <v>13.5</v>
+        <v>10.8</v>
       </c>
       <c r="I27" s="2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3582,16 +3582,16 @@
         <v>33</v>
       </c>
       <c r="E28">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F28">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G28" s="1">
-        <v>45.5</v>
+        <v>42.4</v>
       </c>
       <c r="H28" s="1">
-        <v>54.5</v>
+        <v>57.6</v>
       </c>
       <c r="I28" s="2">
         <v>6.1</v>
@@ -3661,7 +3661,7 @@
         <v>35.9</v>
       </c>
       <c r="I30" s="2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -3678,16 +3678,16 @@
         <v>647</v>
       </c>
       <c r="E31">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="F31">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="G31" s="1">
-        <v>81</v>
+        <v>78.8</v>
       </c>
       <c r="H31" s="1">
-        <v>19</v>
+        <v>21.2</v>
       </c>
       <c r="I31" s="2">
         <v>7.5</v>

--- a/academias/Electricidad - Estadisticos 20222.xlsx
+++ b/academias/Electricidad - Estadisticos 20222.xlsx
@@ -1621,25 +1621,25 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1656,25 +1656,25 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1688,25 +1688,25 @@
         <v>60</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F4">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J4">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1793,25 +1793,25 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>42.4</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>57.6</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1863,25 +1863,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>27.3</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1895,25 +1895,25 @@
         <v>166</v>
       </c>
       <c r="E10">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="F10">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="G10" s="1">
-        <v>48.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>51.8</v>
+        <v>28.9</v>
       </c>
       <c r="I10" s="2">
-        <v>4.7</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>39.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2606,25 +2606,25 @@
         <v>647</v>
       </c>
       <c r="E31">
-        <v>281</v>
+        <v>379</v>
       </c>
       <c r="F31">
-        <v>366</v>
+        <v>268</v>
       </c>
       <c r="G31" s="1">
-        <v>43.4</v>
+        <v>58.6</v>
       </c>
       <c r="H31" s="1">
-        <v>56.6</v>
+        <v>41.4</v>
       </c>
       <c r="I31" s="2">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="J31">
-        <v>280</v>
+        <v>154</v>
       </c>
       <c r="K31" s="1">
-        <v>43.3</v>
+        <v>23.8</v>
       </c>
     </row>
   </sheetData>
@@ -2705,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2740,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2772,7 +2772,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2865,19 +2865,19 @@
         <v>33</v>
       </c>
       <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
         <v>19</v>
       </c>
-      <c r="F7">
-        <v>14</v>
-      </c>
       <c r="G7" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="H7" s="1">
         <v>57.6</v>
       </c>
-      <c r="H7" s="1">
-        <v>42.4</v>
-      </c>
       <c r="I7" s="2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2967,19 +2967,19 @@
         <v>166</v>
       </c>
       <c r="E10">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F10">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G10" s="1">
-        <v>74.09999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>25.9</v>
+        <v>28.9</v>
       </c>
       <c r="I10" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3678,19 +3678,19 @@
         <v>647</v>
       </c>
       <c r="E31">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="F31">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G31" s="1">
-        <v>78.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H31" s="1">
-        <v>21.2</v>
+        <v>21.9</v>
       </c>
       <c r="I31" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J31">
         <v>0</v>

--- a/academias/Electricidad - Estadisticos 20222.xlsx
+++ b/academias/Electricidad - Estadisticos 20222.xlsx
@@ -1930,25 +1930,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>11.8</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1965,25 +1965,25 @@
         <v>28</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>3.6</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J12">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1997,25 +1997,25 @@
         <v>62</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F13">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>8.1</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2032,25 +2032,25 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F14">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>19.4</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J14">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2099,25 +2099,25 @@
         <v>60</v>
       </c>
       <c r="E16">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F16">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G16" s="1">
-        <v>41.7</v>
+        <v>83.3</v>
       </c>
       <c r="H16" s="1">
-        <v>58.3</v>
+        <v>16.7</v>
       </c>
       <c r="I16" s="2">
-        <v>4</v>
+        <v>8.6</v>
       </c>
       <c r="J16">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="K16" s="1">
-        <v>51.7</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2408,25 +2408,25 @@
         <v>28</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F25">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J25">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2440,25 +2440,25 @@
         <v>28</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F26">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J26">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2606,25 +2606,25 @@
         <v>647</v>
       </c>
       <c r="E31">
-        <v>379</v>
+        <v>487</v>
       </c>
       <c r="F31">
-        <v>268</v>
+        <v>160</v>
       </c>
       <c r="G31" s="1">
-        <v>58.6</v>
+        <v>75.3</v>
       </c>
       <c r="H31" s="1">
-        <v>41.4</v>
+        <v>24.7</v>
       </c>
       <c r="I31" s="2">
-        <v>5.4</v>
+        <v>6.9</v>
       </c>
       <c r="J31">
-        <v>154</v>
+        <v>38</v>
       </c>
       <c r="K31" s="1">
-        <v>23.8</v>
+        <v>5.9</v>
       </c>
     </row>
   </sheetData>
@@ -3002,19 +3002,19 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="H11" s="1">
-        <v>5.9</v>
+        <v>11.8</v>
       </c>
       <c r="I11" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3049,7 +3049,7 @@
         <v>3.6</v>
       </c>
       <c r="I12" s="2">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3069,19 +3069,19 @@
         <v>62</v>
       </c>
       <c r="E13">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>95.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>4.8</v>
+        <v>8.1</v>
       </c>
       <c r="I13" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3104,19 +3104,19 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>74.2</v>
+        <v>93.5</v>
       </c>
       <c r="H14" s="1">
-        <v>25.8</v>
+        <v>6.5</v>
       </c>
       <c r="I14" s="2">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3171,19 +3171,19 @@
         <v>60</v>
       </c>
       <c r="E16">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F16">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G16" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H16" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I16" s="2">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3480,19 +3480,19 @@
         <v>28</v>
       </c>
       <c r="E25">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" s="1">
-        <v>89.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H25" s="1">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="I25" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3512,19 +3512,19 @@
         <v>28</v>
       </c>
       <c r="E26">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1">
-        <v>89.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H26" s="1">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="I26" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3678,19 +3678,19 @@
         <v>647</v>
       </c>
       <c r="E31">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="F31">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G31" s="1">
-        <v>78.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="H31" s="1">
-        <v>21.9</v>
+        <v>21.2</v>
       </c>
       <c r="I31" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J31">
         <v>0</v>

--- a/academias/Electricidad - Estadisticos 20222.xlsx
+++ b/academias/Electricidad - Estadisticos 20222.xlsx
@@ -2032,25 +2032,25 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>80.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>19.4</v>
+        <v>16.1</v>
       </c>
       <c r="I14" s="2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2099,25 +2099,25 @@
         <v>60</v>
       </c>
       <c r="E16">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16" s="1">
-        <v>83.3</v>
+        <v>85</v>
       </c>
       <c r="H16" s="1">
-        <v>16.7</v>
+        <v>15</v>
       </c>
       <c r="I16" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2545,25 +2545,25 @@
         <v>33</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F29">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>60.6</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>39.4</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J29">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2577,25 +2577,25 @@
         <v>103</v>
       </c>
       <c r="E30">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="F30">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="G30" s="1">
-        <v>45.6</v>
+        <v>65</v>
       </c>
       <c r="H30" s="1">
-        <v>54.4</v>
+        <v>35</v>
       </c>
       <c r="I30" s="2">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="J30">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2606,25 +2606,25 @@
         <v>647</v>
       </c>
       <c r="E31">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="F31">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="G31" s="1">
-        <v>75.3</v>
+        <v>78.5</v>
       </c>
       <c r="H31" s="1">
-        <v>24.7</v>
+        <v>21.5</v>
       </c>
       <c r="I31" s="2">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="J31">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>5.9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3104,19 +3104,19 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>93.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>6.5</v>
+        <v>16.1</v>
       </c>
       <c r="I14" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3171,16 +3171,16 @@
         <v>60</v>
       </c>
       <c r="E16">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G16" s="1">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H16" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I16" s="2">
         <v>7.6</v>
@@ -3617,19 +3617,19 @@
         <v>33</v>
       </c>
       <c r="E29">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F29">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29" s="1">
-        <v>57.6</v>
+        <v>60.6</v>
       </c>
       <c r="H29" s="1">
-        <v>42.4</v>
+        <v>39.4</v>
       </c>
       <c r="I29" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -3649,19 +3649,19 @@
         <v>103</v>
       </c>
       <c r="E30">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F30">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G30" s="1">
-        <v>64.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="H30" s="1">
-        <v>35.9</v>
+        <v>35</v>
       </c>
       <c r="I30" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -3678,16 +3678,16 @@
         <v>647</v>
       </c>
       <c r="E31">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F31">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G31" s="1">
-        <v>78.8</v>
+        <v>78.5</v>
       </c>
       <c r="H31" s="1">
-        <v>21.2</v>
+        <v>21.5</v>
       </c>
       <c r="I31" s="2">
         <v>7.5</v>

--- a/academias/Electricidad - Estadisticos 20222.xlsx
+++ b/academias/Electricidad - Estadisticos 20222.xlsx
@@ -1565,8 +1565,7 @@
   <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -2637,8 +2636,7 @@
   <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -2705,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2740,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2795,19 +2793,19 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>85.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>14.7</v>
+        <v>17.6</v>
       </c>
       <c r="I5" s="2">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2830,19 +2828,19 @@
         <v>37</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1">
-        <v>70.3</v>
+        <v>75.7</v>
       </c>
       <c r="H6" s="1">
-        <v>29.7</v>
+        <v>24.3</v>
       </c>
       <c r="I6" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2865,19 +2863,19 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1">
-        <v>42.4</v>
+        <v>66.7</v>
       </c>
       <c r="H7" s="1">
-        <v>57.6</v>
+        <v>33.3</v>
       </c>
       <c r="I7" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2900,19 +2898,19 @@
         <v>29</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>86.2</v>
+        <v>82.8</v>
       </c>
       <c r="H8" s="1">
-        <v>13.8</v>
+        <v>17.2</v>
       </c>
       <c r="I8" s="2">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2935,19 +2933,19 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1">
-        <v>72.7</v>
+        <v>78.8</v>
       </c>
       <c r="H9" s="1">
-        <v>27.3</v>
+        <v>21.2</v>
       </c>
       <c r="I9" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2967,19 +2965,19 @@
         <v>166</v>
       </c>
       <c r="E10">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F10">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G10" s="1">
-        <v>71.09999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>28.9</v>
+        <v>22.9</v>
       </c>
       <c r="I10" s="2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3002,19 +3000,19 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>11.8</v>
+        <v>5.9</v>
       </c>
       <c r="I11" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3037,19 +3035,19 @@
         <v>28</v>
       </c>
       <c r="E12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3069,19 +3067,19 @@
         <v>62</v>
       </c>
       <c r="E13">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>91.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="H13" s="1">
-        <v>8.1</v>
+        <v>3.2</v>
       </c>
       <c r="I13" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3104,19 +3102,19 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>83.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="H14" s="1">
-        <v>16.1</v>
+        <v>3.2</v>
       </c>
       <c r="I14" s="2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3139,19 +3137,19 @@
         <v>29</v>
       </c>
       <c r="E15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>86.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>13.8</v>
+        <v>6.9</v>
       </c>
       <c r="I15" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3171,19 +3169,19 @@
         <v>60</v>
       </c>
       <c r="E16">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F16">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H16" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I16" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3343,19 +3341,19 @@
         <v>31</v>
       </c>
       <c r="E21">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>93.5</v>
+        <v>96.8</v>
       </c>
       <c r="H21" s="1">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="I21" s="2">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3378,19 +3376,19 @@
         <v>31</v>
       </c>
       <c r="E22">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>93.5</v>
+        <v>96.8</v>
       </c>
       <c r="H22" s="1">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="I22" s="2">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3413,19 +3411,19 @@
         <v>29</v>
       </c>
       <c r="E23">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F23">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>58.6</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>41.4</v>
+        <v>3.4</v>
       </c>
       <c r="I23" s="2">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3445,19 +3443,19 @@
         <v>91</v>
       </c>
       <c r="E24">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="F24">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G24" s="1">
-        <v>82.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="H24" s="1">
-        <v>17.6</v>
+        <v>3.3</v>
       </c>
       <c r="I24" s="2">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3480,19 +3478,19 @@
         <v>28</v>
       </c>
       <c r="E25">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>92.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3512,19 +3510,19 @@
         <v>28</v>
       </c>
       <c r="E26">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>92.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3582,19 +3580,19 @@
         <v>33</v>
       </c>
       <c r="E28">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F28">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G28" s="1">
-        <v>42.4</v>
+        <v>63.6</v>
       </c>
       <c r="H28" s="1">
-        <v>57.6</v>
+        <v>36.4</v>
       </c>
       <c r="I28" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3649,16 +3647,16 @@
         <v>103</v>
       </c>
       <c r="E30">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F30">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G30" s="1">
-        <v>65</v>
+        <v>71.8</v>
       </c>
       <c r="H30" s="1">
-        <v>35</v>
+        <v>28.2</v>
       </c>
       <c r="I30" s="2">
         <v>6.7</v>
@@ -3678,16 +3676,16 @@
         <v>647</v>
       </c>
       <c r="E31">
-        <v>508</v>
+        <v>549</v>
       </c>
       <c r="F31">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="G31" s="1">
-        <v>78.5</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>21.5</v>
+        <v>15.1</v>
       </c>
       <c r="I31" s="2">
         <v>7.5</v>

--- a/academias/Electricidad - Estadisticos 20222.xlsx
+++ b/academias/Electricidad - Estadisticos 20222.xlsx
@@ -3204,19 +3204,19 @@
         <v>33</v>
       </c>
       <c r="E17">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F17">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1">
-        <v>66.7</v>
+        <v>84.8</v>
       </c>
       <c r="H17" s="1">
-        <v>33.3</v>
+        <v>15.2</v>
       </c>
       <c r="I17" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3239,19 +3239,19 @@
         <v>22</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>68.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>31.8</v>
+        <v>13.6</v>
       </c>
       <c r="I18" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3274,16 +3274,16 @@
         <v>22</v>
       </c>
       <c r="E19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>77.3</v>
+        <v>81.8</v>
       </c>
       <c r="H19" s="1">
-        <v>22.7</v>
+        <v>18.2</v>
       </c>
       <c r="I19" s="2">
         <v>6.3</v>
@@ -3306,19 +3306,19 @@
         <v>77</v>
       </c>
       <c r="E20">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="F20">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G20" s="1">
-        <v>70.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>29.9</v>
+        <v>15.6</v>
       </c>
       <c r="I20" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3545,19 +3545,19 @@
         <v>37</v>
       </c>
       <c r="E27">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G27" s="1">
-        <v>89.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H27" s="1">
-        <v>10.8</v>
+        <v>21.6</v>
       </c>
       <c r="I27" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3647,16 +3647,16 @@
         <v>103</v>
       </c>
       <c r="E30">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F30">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G30" s="1">
-        <v>71.8</v>
+        <v>68</v>
       </c>
       <c r="H30" s="1">
-        <v>28.2</v>
+        <v>32</v>
       </c>
       <c r="I30" s="2">
         <v>6.7</v>
@@ -3676,16 +3676,16 @@
         <v>647</v>
       </c>
       <c r="E31">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="F31">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G31" s="1">
-        <v>84.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>15.1</v>
+        <v>14.1</v>
       </c>
       <c r="I31" s="2">
         <v>7.5</v>

--- a/academias/Electricidad - Estadisticos 20222.xlsx
+++ b/academias/Electricidad - Estadisticos 20222.xlsx
@@ -3615,19 +3615,19 @@
         <v>33</v>
       </c>
       <c r="E29">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F29">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G29" s="1">
-        <v>60.6</v>
+        <v>81.8</v>
       </c>
       <c r="H29" s="1">
-        <v>39.4</v>
+        <v>18.2</v>
       </c>
       <c r="I29" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -3647,19 +3647,19 @@
         <v>103</v>
       </c>
       <c r="E30">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F30">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G30" s="1">
-        <v>68</v>
+        <v>74.8</v>
       </c>
       <c r="H30" s="1">
-        <v>32</v>
+        <v>25.2</v>
       </c>
       <c r="I30" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -3676,16 +3676,16 @@
         <v>647</v>
       </c>
       <c r="E31">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="F31">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G31" s="1">
-        <v>85.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="H31" s="1">
-        <v>14.1</v>
+        <v>13</v>
       </c>
       <c r="I31" s="2">
         <v>7.5</v>
